--- a/data-sources/tonewood-species.xlsx
+++ b/data-sources/tonewood-species.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BCQPpHU8QnuHLEUmfTxQYcdDztAuUlsDsRhdvm4nLoU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6wfTZGtTgExQbfLqd+tnDhV+0sWl2wSgUesvFZno8vw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="511">
   <si>
     <t>TONEWOOD SPECIES - NAMING REFERENCE</t>
   </si>
@@ -270,6 +270,9 @@
     <t>African Okoume</t>
   </si>
   <si>
+    <t>Africa</t>
+  </si>
+  <si>
     <t>Betula pendula</t>
   </si>
   <si>
@@ -531,25 +534,22 @@
     <t>Indian Rosewood</t>
   </si>
   <si>
+    <t>Indonesian Rosewood</t>
+  </si>
+  <si>
     <t>Indisk Rosenträ</t>
   </si>
   <si>
+    <t>Indonesisk Rosenträ</t>
+  </si>
+  <si>
     <t>Pau-Rosa Indiano</t>
   </si>
   <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Indonesian Rosewood</t>
-  </si>
-  <si>
-    <t>Indonesisk Rosenträ</t>
-  </si>
-  <si>
     <t>Pau-Rosa Indonésio</t>
   </si>
   <si>
-    <t>Indonesia</t>
+    <t>India, Indonesia</t>
   </si>
   <si>
     <t>Dalbergia melanoxylon</t>
@@ -573,6 +573,36 @@
     <t>Central America (Costa Rica, Panama)</t>
   </si>
   <si>
+    <t>Dalbergia spruceana</t>
+  </si>
+  <si>
+    <t>Amazon Rosewood</t>
+  </si>
+  <si>
+    <t>Amazon Rosenträ</t>
+  </si>
+  <si>
+    <t>Pau-Rosa do Amazonas</t>
+  </si>
+  <si>
+    <t>Brazil (Amazon)</t>
+  </si>
+  <si>
+    <t>Dalbergia baronii</t>
+  </si>
+  <si>
+    <t>Madagascar Rosewood</t>
+  </si>
+  <si>
+    <t>Madagaskar Rosenträ</t>
+  </si>
+  <si>
+    <t>Pau-Rosa de Madagascar</t>
+  </si>
+  <si>
+    <t>Madagascar</t>
+  </si>
+  <si>
     <t>Diospyros celebica</t>
   </si>
   <si>
@@ -627,6 +657,9 @@
     <t>Ébano da Malasia</t>
   </si>
   <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
     <t>Entandrophragma cylindricum</t>
   </si>
   <si>
@@ -732,6 +765,18 @@
     <t>Freixo Negro</t>
   </si>
   <si>
+    <t>Guibourtia demeusei</t>
+  </si>
+  <si>
+    <t>Bubinga</t>
+  </si>
+  <si>
+    <t>Bosse Cedar</t>
+  </si>
+  <si>
+    <t>West Africa</t>
+  </si>
+  <si>
     <t>Guibourtia ehie</t>
   </si>
   <si>
@@ -744,16 +789,10 @@
     <t>West Africa (Ivory Coast, Ghana)</t>
   </si>
   <si>
-    <t>Guibourtia demeusei</t>
-  </si>
-  <si>
-    <t>Bubinga</t>
-  </si>
-  <si>
-    <t>Bosse Cedar</t>
-  </si>
-  <si>
-    <t>West Africa</t>
+    <t>Guibourtia spp.</t>
+  </si>
+  <si>
+    <t>African Bosse Cedar</t>
   </si>
   <si>
     <t>Handroanthus spp.</t>
@@ -939,6 +978,18 @@
     <t>Central Africa (Congo, Cameroon)</t>
   </si>
   <si>
+    <t>Mixed species</t>
+  </si>
+  <si>
+    <t>Mixpall ädelträ</t>
+  </si>
+  <si>
+    <t>Espécies variadas</t>
+  </si>
+  <si>
+    <t>Various</t>
+  </si>
+  <si>
     <t>Olea europaea</t>
   </si>
   <si>
@@ -1350,6 +1401,9 @@
     <t>Mogno das Honduras</t>
   </si>
   <si>
+    <t>Honduras</t>
+  </si>
+  <si>
     <t>Taxus baccata</t>
   </si>
   <si>
@@ -1491,13 +1545,10 @@
     <t>Olmo</t>
   </si>
   <si>
-    <t>Mixed species</t>
-  </si>
-  <si>
-    <t>Mixpall ädelträ</t>
-  </si>
-  <si>
-    <t>Espécies variadas</t>
+    <t>Various species</t>
+  </si>
+  <si>
+    <t>Olika arter</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1631,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1625,6 +1676,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2502,7 +2556,9 @@
         <v>82</v>
       </c>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+      <c r="J15" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="K15" s="8"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2526,28 +2582,28 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="2"/>
@@ -2572,28 +2628,28 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="2"/>
@@ -2618,28 +2674,28 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="2"/>
@@ -2664,28 +2720,28 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="2"/>
@@ -2710,33 +2766,33 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>111</v>
-      </c>
       <c r="E20" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2760,26 +2816,26 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="2"/>
@@ -2804,24 +2860,24 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8" t="s">
@@ -2850,26 +2906,26 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="2"/>
@@ -2894,25 +2950,27 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="J24" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="K24" s="8"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2936,26 +2994,26 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="2"/>
@@ -2980,26 +3038,26 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K26" s="8"/>
       <c r="L26" s="2"/>
@@ -3024,24 +3082,24 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="8" t="s">
@@ -3070,24 +3128,24 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8" t="s">
@@ -3116,33 +3174,33 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>157</v>
-      </c>
       <c r="E29" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8" t="s">
         <v>80</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -3166,33 +3224,33 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>164</v>
-      </c>
       <c r="E30" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="8" t="s">
         <v>80</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -3216,29 +3274,37 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C31" s="8"/>
+        <v>171</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="D31" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" s="9"/>
+        <v>171</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="F31" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="8"/>
+        <v>173</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="H31" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -3261,31 +3327,29 @@
       <c r="AD31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>174</v>
+      <c r="A32" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>179</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="8" t="s">
-        <v>174</v>
+      <c r="D32" s="16" t="s">
+        <v>179</v>
       </c>
       <c r="E32" s="8"/>
-      <c r="F32" s="8" t="s">
-        <v>175</v>
+      <c r="F32" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="G32" s="8"/>
-      <c r="H32" s="8" t="s">
-        <v>176</v>
+      <c r="H32" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="I32" s="8"/>
-      <c r="J32" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>162</v>
-      </c>
+      <c r="J32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="8"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -3307,27 +3371,31 @@
       <c r="AD32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>179</v>
+      <c r="A33" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="16" t="s">
-        <v>179</v>
+      <c r="D33" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="E33" s="8"/>
-      <c r="F33" s="9" t="s">
-        <v>180</v>
+      <c r="F33" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="G33" s="8"/>
-      <c r="H33" s="9" t="s">
-        <v>181</v>
+      <c r="H33" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
+      <c r="J33" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -3349,30 +3417,30 @@
       <c r="AD33" s="2"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>162</v>
+      <c r="A34" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>118</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -3395,31 +3463,31 @@
       <c r="AD34" s="2"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8" t="s">
+      <c r="A35" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="K35" s="8"/>
+      <c r="B35" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>163</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -3442,28 +3510,28 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="2"/>
@@ -3487,30 +3555,30 @@
       <c r="AD36" s="2"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>201</v>
       </c>
+      <c r="B37" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>204</v>
+      </c>
       <c r="G37" s="8"/>
-      <c r="H37" s="9" t="s">
-        <v>202</v>
+      <c r="H37" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
+      <c r="J37" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="K37" s="8"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -3533,26 +3601,32 @@
       <c r="AD37" s="2"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="E38" s="9"/>
+      <c r="A38" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>210</v>
+      </c>
       <c r="F38" s="9" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="9" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
+      <c r="J38" s="9" t="s">
+        <v>213</v>
+      </c>
       <c r="K38" s="8"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -3575,29 +3649,27 @@
       <c r="AD38" s="2"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>207</v>
+      <c r="A39" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>207</v>
+      <c r="D39" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9" t="s">
+        <v>216</v>
       </c>
       <c r="G39" s="8"/>
-      <c r="H39" s="8" t="s">
-        <v>207</v>
+      <c r="H39" s="9" t="s">
+        <v>216</v>
       </c>
       <c r="I39" s="8"/>
-      <c r="J39" s="8" t="s">
-        <v>209</v>
+      <c r="J39" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="2"/>
@@ -3622,26 +3694,28 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C40" s="8"/>
-      <c r="D40" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E40" s="8"/>
+      <c r="D40" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>219</v>
+      </c>
       <c r="F40" s="8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I40" s="8"/>
       <c r="J40" s="8" t="s">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="K40" s="8"/>
       <c r="L40" s="2"/>
@@ -3666,26 +3740,26 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I41" s="8"/>
       <c r="J41" s="8" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="2"/>
@@ -3709,27 +3783,27 @@
       <c r="AD41" s="2"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>220</v>
+      <c r="A42" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="C42" s="8"/>
-      <c r="D42" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9" t="s">
-        <v>221</v>
+      <c r="D42" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="G42" s="8"/>
-      <c r="H42" s="9" t="s">
-        <v>222</v>
+      <c r="H42" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="I42" s="8"/>
-      <c r="J42" s="9" t="s">
-        <v>223</v>
+      <c r="J42" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="2"/>
@@ -3753,29 +3827,27 @@
       <c r="AD42" s="2"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>225</v>
+      <c r="A43" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>231</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>227</v>
+      <c r="D43" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>232</v>
       </c>
       <c r="G43" s="8"/>
-      <c r="H43" s="8" t="s">
-        <v>228</v>
+      <c r="H43" s="9" t="s">
+        <v>233</v>
       </c>
       <c r="I43" s="8"/>
-      <c r="J43" s="8" t="s">
-        <v>229</v>
+      <c r="J43" s="9" t="s">
+        <v>234</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="2"/>
@@ -3800,26 +3872,28 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>231</v>
+        <v>235</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>236</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="E44" s="9"/>
+        <v>236</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="F44" s="8" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8" t="s">
-        <v>34</v>
+        <v>240</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="2"/>
@@ -3844,28 +3918,26 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>235</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="E45" s="9"/>
       <c r="F45" s="8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="2"/>
@@ -3890,28 +3962,28 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8" t="s">
-        <v>241</v>
+        <v>50</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="2"/>
@@ -3936,28 +4008,28 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="15" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>243</v>
+        <v>251</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>250</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="13" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="13" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="2"/>
@@ -3982,32 +4054,30 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>247</v>
+        <v>253</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E48" s="9"/>
+        <v>254</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>255</v>
+      </c>
       <c r="F48" s="8" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G48" s="8"/>
-      <c r="H48" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>249</v>
-      </c>
+      <c r="H48" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I48" s="8"/>
       <c r="J48" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>162</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="K48" s="8"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -4029,29 +4099,29 @@
       <c r="AD48" s="2"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="9" t="s">
+      <c r="C49" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="E49" s="9"/>
+      <c r="F49" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="G49" s="8"/>
+      <c r="H49" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="I49" s="8"/>
+      <c r="J49" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="2"/>
@@ -4076,30 +4146,32 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>258</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="E50" s="9"/>
       <c r="F50" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G50" s="8"/>
-      <c r="H50" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="I50" s="8"/>
+      <c r="H50" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>262</v>
+      </c>
       <c r="J50" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K50" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -4122,28 +4194,28 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="8" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K51" s="8"/>
       <c r="L51" s="2"/>
@@ -4168,32 +4240,30 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="C52" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="E52" s="8"/>
+      <c r="B52" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>271</v>
+      </c>
       <c r="F52" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>162</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="K52" s="8"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -4216,26 +4286,28 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C53" s="8"/>
-      <c r="D53" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E53" s="8"/>
+      <c r="D53" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>277</v>
+      </c>
       <c r="F53" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8" t="s">
-        <v>277</v>
+        <v>34</v>
       </c>
       <c r="K53" s="8"/>
       <c r="L53" s="2"/>
@@ -4260,30 +4332,32 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>280</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E54" s="8"/>
       <c r="F54" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K54" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
@@ -4305,29 +4379,27 @@
       <c r="AD54" s="2"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="C55" s="9" t="s">
+      <c r="A55" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="16" t="s">
-        <v>284</v>
+      <c r="B55" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="G55" s="8"/>
-      <c r="H55" s="16" t="s">
-        <v>284</v>
+      <c r="H55" s="8" t="s">
+        <v>289</v>
       </c>
       <c r="I55" s="8"/>
-      <c r="J55" s="9" t="s">
-        <v>80</v>
+      <c r="J55" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="K55" s="8"/>
       <c r="L55" s="2"/>
@@ -4351,28 +4423,30 @@
       <c r="AD55" s="2"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="E56" s="9"/>
+      <c r="A56" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>293</v>
+      </c>
       <c r="F56" s="8" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G56" s="8"/>
-      <c r="H56" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="8"/>
+      <c r="H56" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="K56" s="8"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -4395,28 +4469,28 @@
       <c r="AD56" s="2"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="C57" s="8"/>
+      <c r="A57" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="D57" s="9" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="E57" s="9"/>
-      <c r="F57" s="8" t="s">
-        <v>289</v>
+      <c r="F57" s="16" t="s">
+        <v>297</v>
       </c>
       <c r="G57" s="8"/>
-      <c r="H57" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="J57" s="8" t="s">
+      <c r="H57" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I57" s="8"/>
+      <c r="J57" s="9" t="s">
         <v>80</v>
       </c>
       <c r="K57" s="8"/>
@@ -4441,27 +4515,29 @@
       <c r="AD57" s="2"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E58" s="8"/>
+      <c r="A58" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E58" s="9"/>
       <c r="F58" s="8" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G58" s="8"/>
-      <c r="H58" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8" t="s">
-        <v>297</v>
+      <c r="H58" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="2"/>
@@ -4486,28 +4562,28 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C59" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="E59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E59" s="9"/>
       <c r="F59" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G59" s="8"/>
-      <c r="H59" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="I59" s="8"/>
+      <c r="H59" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>305</v>
+      </c>
       <c r="J59" s="8" t="s">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="2"/>
@@ -4532,28 +4608,26 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>304</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="2"/>
@@ -4578,30 +4652,28 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>310</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8" t="s">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="2"/>
@@ -4626,28 +4698,28 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>315</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E62" s="8"/>
       <c r="F62" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8" t="s">
-        <v>73</v>
+        <v>319</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="2"/>
@@ -4671,29 +4743,26 @@
       <c r="AD62" s="2"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>319</v>
+      <c r="A63" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>320</v>
       </c>
       <c r="C63" s="8"/>
-      <c r="D63" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="E63" s="9" t="s">
+      <c r="D63" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="E63" s="8"/>
+      <c r="F63" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="9" t="s">
         <v>322</v>
       </c>
       <c r="I63" s="8"/>
-      <c r="J63" s="8" t="s">
-        <v>116</v>
+      <c r="J63" s="9" t="s">
+        <v>323</v>
       </c>
       <c r="K63" s="8"/>
       <c r="L63" s="2"/>
@@ -4718,26 +4787,30 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="E64" s="8"/>
+      <c r="C64" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>327</v>
+      </c>
       <c r="F64" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G64" s="8"/>
       <c r="H64" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="8" t="s">
-        <v>328</v>
+        <v>73</v>
       </c>
       <c r="K64" s="8"/>
       <c r="L64" s="2"/>
@@ -4762,26 +4835,28 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C65" s="8"/>
-      <c r="D65" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="E65" s="8"/>
+      <c r="D65" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>332</v>
+      </c>
       <c r="F65" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8" t="s">
-        <v>333</v>
+        <v>73</v>
       </c>
       <c r="K65" s="8"/>
       <c r="L65" s="2"/>
@@ -4806,28 +4881,28 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8" t="s">
-        <v>339</v>
+        <v>117</v>
       </c>
       <c r="K66" s="8"/>
       <c r="L66" s="2"/>
@@ -4851,26 +4926,28 @@
       <c r="AD66" s="2"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9" t="s">
+      <c r="C67" s="8"/>
+      <c r="D67" s="8" t="s">
         <v>342</v>
       </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8" t="s">
+        <v>343</v>
+      </c>
       <c r="G67" s="8"/>
-      <c r="H67" s="9" t="s">
-        <v>343</v>
+      <c r="H67" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
+      <c r="J67" s="8" t="s">
+        <v>345</v>
+      </c>
       <c r="K67" s="8"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -4894,28 +4971,26 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C68" s="8"/>
-      <c r="D68" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>346</v>
-      </c>
+      <c r="D68" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="E68" s="8"/>
       <c r="F68" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K68" s="8"/>
       <c r="L68" s="2"/>
@@ -4940,28 +5015,28 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G69" s="8"/>
       <c r="H69" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I69" s="8"/>
       <c r="J69" s="8" t="s">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="K69" s="8"/>
       <c r="L69" s="2"/>
@@ -4986,25 +5061,27 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="C70" s="9"/>
-      <c r="D70" s="17" t="s">
-        <v>356</v>
+      <c r="D70" s="18" t="s">
+        <v>358</v>
       </c>
       <c r="E70" s="9"/>
       <c r="F70" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G70" s="8"/>
       <c r="H70" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
+      <c r="J70" s="9" t="s">
+        <v>234</v>
+      </c>
       <c r="K70" s="8"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -5028,30 +5105,28 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C71" s="9" t="s">
         <v>361</v>
       </c>
+      <c r="B71" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C71" s="8"/>
       <c r="D71" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G71" s="8"/>
       <c r="H71" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K71" s="8"/>
       <c r="L71" s="2"/>
@@ -5075,27 +5150,29 @@
       <c r="AD71" s="2"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>366</v>
+      <c r="A72" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>368</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9" t="s">
         <v>368</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8" t="s">
+        <v>371</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="8" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="K72" s="8"/>
       <c r="L72" s="2"/>
@@ -5120,26 +5197,26 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="18" t="s">
+        <v>373</v>
       </c>
       <c r="E73" s="9"/>
       <c r="F73" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="G73" s="9"/>
-      <c r="H73" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
+      </c>
+      <c r="G73" s="8"/>
+      <c r="H73" s="9" t="s">
+        <v>375</v>
       </c>
       <c r="I73" s="8"/>
-      <c r="J73" s="8" t="s">
-        <v>43</v>
+      <c r="J73" s="9" t="s">
+        <v>234</v>
       </c>
       <c r="K73" s="8"/>
       <c r="L73" s="2"/>
@@ -5164,25 +5241,31 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="E74" s="9"/>
+        <v>376</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>378</v>
+      </c>
       <c r="F74" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9" t="s">
-        <v>373</v>
+        <v>379</v>
+      </c>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8" t="s">
+        <v>380</v>
       </c>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
+      <c r="J74" s="8" t="s">
+        <v>381</v>
+      </c>
       <c r="K74" s="8"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -5205,27 +5288,27 @@
       <c r="AD74" s="2"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>377</v>
+      <c r="A75" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>383</v>
       </c>
       <c r="C75" s="8"/>
-      <c r="D75" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8" t="s">
-        <v>380</v>
+      <c r="D75" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9" t="s">
+        <v>385</v>
       </c>
       <c r="I75" s="8"/>
       <c r="J75" s="8" t="s">
-        <v>381</v>
+        <v>43</v>
       </c>
       <c r="K75" s="8"/>
       <c r="L75" s="2"/>
@@ -5249,25 +5332,23 @@
       <c r="AD75" s="2"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="7" t="s">
-        <v>382</v>
+      <c r="A76" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="G76" s="8"/>
+        <v>388</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="G76" s="9"/>
       <c r="H76" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="8" t="s">
@@ -5296,28 +5377,26 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C77" s="8"/>
-      <c r="D77" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E77" s="9" t="s">
+      <c r="D77" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="E77" s="9"/>
+      <c r="F77" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F77" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8" t="s">
-        <v>392</v>
-      </c>
       <c r="I77" s="8"/>
-      <c r="J77" s="8" t="s">
-        <v>393</v>
+      <c r="J77" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="K77" s="8"/>
       <c r="L77" s="2"/>
@@ -5342,16 +5421,14 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="C78" s="8"/>
+      <c r="D78" s="8" t="s">
         <v>395</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>397</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8" t="s">
@@ -5359,15 +5436,13 @@
       </c>
       <c r="G78" s="8"/>
       <c r="H78" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="K78" s="8" t="s">
-        <v>162</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="K78" s="8"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -5390,24 +5465,24 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G79" s="8"/>
       <c r="H79" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8" t="s">
@@ -5436,26 +5511,28 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C80" s="8"/>
-      <c r="D80" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="E80" s="8"/>
+      <c r="D80" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>407</v>
+      </c>
       <c r="F80" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G80" s="8"/>
       <c r="H80" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I80" s="8"/>
       <c r="J80" s="8" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="K80" s="8"/>
       <c r="L80" s="2"/>
@@ -5480,20 +5557,20 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>410</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="E81" s="8"/>
       <c r="F81" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G81" s="8"/>
       <c r="H81" s="8" t="s">
@@ -5501,9 +5578,11 @@
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K81" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -5525,23 +5604,25 @@
       <c r="AD81" s="2"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="12" t="s">
-        <v>413</v>
+      <c r="A82" s="7" t="s">
+        <v>415</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="G82" s="9"/>
+        <v>417</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="G82" s="8"/>
       <c r="H82" s="8" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="I82" s="8"/>
       <c r="J82" s="8" t="s">
@@ -5570,26 +5651,26 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="7" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E83" s="8"/>
       <c r="F83" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G83" s="8"/>
       <c r="H83" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="8" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="K83" s="8"/>
       <c r="L83" s="2"/>
@@ -5613,27 +5694,29 @@
       <c r="AD83" s="2"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="12" t="s">
-        <v>423</v>
+      <c r="A84" s="7" t="s">
+        <v>425</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="G84" s="9"/>
+        <v>426</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="G84" s="8"/>
       <c r="H84" s="8" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="I84" s="8"/>
       <c r="J84" s="8" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="K84" s="8"/>
       <c r="L84" s="2"/>
@@ -5657,27 +5740,27 @@
       <c r="AD84" s="2"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="7" t="s">
-        <v>426</v>
+      <c r="A85" s="12" t="s">
+        <v>430</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C85" s="8"/>
-      <c r="D85" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="G85" s="8"/>
+      <c r="D85" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G85" s="9"/>
       <c r="H85" s="8" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="8" t="s">
-        <v>430</v>
+        <v>43</v>
       </c>
       <c r="K85" s="8"/>
       <c r="L85" s="2"/>
@@ -5702,26 +5785,26 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E86" s="8"/>
       <c r="F86" s="8" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="G86" s="8"/>
       <c r="H86" s="8" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="I86" s="8"/>
       <c r="J86" s="8" t="s">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="K86" s="8"/>
       <c r="L86" s="2"/>
@@ -5745,29 +5828,27 @@
       <c r="AD86" s="2"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="B87" s="9" t="s">
+      <c r="A87" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="C87" s="8"/>
+      <c r="D87" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="G87" s="9"/>
+      <c r="H87" s="8" t="s">
         <v>434</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8" t="s">
-        <v>437</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K87" s="8"/>
       <c r="L87" s="2"/>
@@ -5792,26 +5873,26 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="8" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G88" s="8"/>
       <c r="H88" s="8" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="8" t="s">
-        <v>245</v>
+        <v>447</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88" s="2"/>
@@ -5835,26 +5916,28 @@
       <c r="AD88" s="2"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>441</v>
+      <c r="A89" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="C89" s="8"/>
-      <c r="D89" s="13" t="s">
-        <v>441</v>
+      <c r="D89" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="E89" s="8"/>
-      <c r="F89" s="9" t="s">
-        <v>442</v>
+      <c r="F89" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="G89" s="8"/>
-      <c r="H89" s="9" t="s">
-        <v>443</v>
+      <c r="H89" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
+      <c r="J89" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="K89" s="8"/>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -5878,28 +5961,28 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C90" s="8"/>
+        <v>450</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>452</v>
+      </c>
       <c r="D90" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>447</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="E90" s="8"/>
       <c r="F90" s="8" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="G90" s="8"/>
       <c r="H90" s="8" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="I90" s="8"/>
       <c r="J90" s="8" t="s">
-        <v>450</v>
+        <v>34</v>
       </c>
       <c r="K90" s="8"/>
       <c r="L90" s="2"/>
@@ -5924,30 +6007,26 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>454</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="E91" s="8"/>
       <c r="F91" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="8" t="s">
-        <v>116</v>
+        <v>252</v>
       </c>
       <c r="K91" s="8"/>
       <c r="L91" s="2"/>
@@ -5971,31 +6050,27 @@
       <c r="AD91" s="2"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="C92" s="9" t="s">
+      <c r="A92" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="F92" s="8" t="s">
+      <c r="B92" s="13" t="s">
         <v>458</v>
       </c>
+      <c r="C92" s="8"/>
+      <c r="D92" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="9" t="s">
+        <v>459</v>
+      </c>
       <c r="G92" s="8"/>
-      <c r="H92" s="8" t="s">
-        <v>458</v>
+      <c r="H92" s="9" t="s">
+        <v>460</v>
       </c>
       <c r="I92" s="8"/>
-      <c r="J92" s="8" t="s">
-        <v>209</v>
+      <c r="J92" s="9" t="s">
+        <v>461</v>
       </c>
       <c r="K92" s="8"/>
       <c r="L92" s="2"/>
@@ -6020,28 +6095,28 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="9" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="G93" s="8"/>
       <c r="H93" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K93" s="8"/>
       <c r="L93" s="2"/>
@@ -6066,28 +6141,30 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="E94" s="8"/>
+        <v>471</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>472</v>
+      </c>
       <c r="F94" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G94" s="8"/>
       <c r="H94" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="8" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="K94" s="8"/>
       <c r="L94" s="2"/>
@@ -6112,22 +6189,22 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="C95" s="13" t="s">
         <v>473</v>
       </c>
+      <c r="B95" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>475</v>
+      </c>
       <c r="D95" s="9" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G95" s="8"/>
       <c r="H95" s="8" t="s">
@@ -6135,7 +6212,7 @@
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="8" t="s">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="K95" s="8"/>
       <c r="L95" s="2"/>
@@ -6167,21 +6244,21 @@
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G96" s="8"/>
       <c r="H96" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="8" t="s">
-        <v>43</v>
+        <v>483</v>
       </c>
       <c r="K96" s="8"/>
       <c r="L96" s="2"/>
@@ -6205,26 +6282,30 @@
       <c r="AD96" s="2"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="B97" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="C97" s="8"/>
-      <c r="D97" s="10" t="s">
+      <c r="A97" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="E97" s="9"/>
-      <c r="F97" s="13" t="s">
-        <v>483</v>
+      <c r="B97" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8" t="s">
+        <v>487</v>
       </c>
       <c r="G97" s="8"/>
-      <c r="H97" s="13" t="s">
-        <v>483</v>
+      <c r="H97" s="8" t="s">
+        <v>488</v>
       </c>
       <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
+      <c r="J97" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="K97" s="8"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -6248,28 +6329,30 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="7" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="C98" s="8"/>
+        <v>490</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>491</v>
+      </c>
       <c r="D98" s="9" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G98" s="8"/>
       <c r="H98" s="8" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I98" s="8"/>
       <c r="J98" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K98" s="8"/>
       <c r="L98" s="2"/>
@@ -6293,25 +6376,30 @@
       <c r="AD98" s="2"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>491</v>
+      <c r="A99" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>496</v>
       </c>
       <c r="C99" s="8"/>
-      <c r="D99" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="E99" s="8"/>
-      <c r="F99" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>493</v>
+      <c r="D99" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8" t="s">
+        <v>499</v>
       </c>
       <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
+      <c r="J99" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="K99" s="8"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -6334,17 +6422,29 @@
       <c r="AD99" s="2"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="20"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
+      <c r="A100" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="C100" s="8"/>
+      <c r="D100" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="G100" s="8"/>
+      <c r="H100" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="I100" s="8"/>
+      <c r="J100" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K100" s="8"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -6366,17 +6466,31 @@
       <c r="AD100" s="2"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="20"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
+      <c r="A101" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="C101" s="8"/>
+      <c r="D101" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K101" s="8"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -6398,16 +6512,30 @@
       <c r="AD101" s="2"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="20"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="A102" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B102" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>509</v>
+      </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
+      <c r="F102" s="11" t="s">
+        <v>510</v>
+      </c>
       <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
+      <c r="H102" s="17" t="s">
+        <v>322</v>
+      </c>
       <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
+      <c r="J102" s="17" t="s">
+        <v>323</v>
+      </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -6430,7 +6558,7 @@
       <c r="AD102" s="2"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="20"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -6462,7 +6590,7 @@
       <c r="AD103" s="2"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="20"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -6494,7 +6622,7 @@
       <c r="AD104" s="2"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="20"/>
+      <c r="A105" s="21"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -6526,7 +6654,7 @@
       <c r="AD105" s="2"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="20"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -6558,7 +6686,7 @@
       <c r="AD106" s="2"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="20"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -6590,7 +6718,7 @@
       <c r="AD107" s="2"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="20"/>
+      <c r="A108" s="21"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -6622,7 +6750,7 @@
       <c r="AD108" s="2"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="20"/>
+      <c r="A109" s="21"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -6654,7 +6782,7 @@
       <c r="AD109" s="2"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="20"/>
+      <c r="A110" s="21"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -6686,7 +6814,7 @@
       <c r="AD110" s="2"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="20"/>
+      <c r="A111" s="21"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -6718,7 +6846,7 @@
       <c r="AD111" s="2"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="20"/>
+      <c r="A112" s="21"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -6750,7 +6878,7 @@
       <c r="AD112" s="2"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="20"/>
+      <c r="A113" s="21"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -6782,7 +6910,7 @@
       <c r="AD113" s="2"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="20"/>
+      <c r="A114" s="21"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -6814,7 +6942,7 @@
       <c r="AD114" s="2"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="20"/>
+      <c r="A115" s="21"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -6846,7 +6974,7 @@
       <c r="AD115" s="2"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="20"/>
+      <c r="A116" s="21"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -6878,7 +7006,7 @@
       <c r="AD116" s="2"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="20"/>
+      <c r="A117" s="21"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -6910,7 +7038,7 @@
       <c r="AD117" s="2"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="20"/>
+      <c r="A118" s="21"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -6942,7 +7070,7 @@
       <c r="AD118" s="2"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="20"/>
+      <c r="A119" s="21"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -6974,7 +7102,7 @@
       <c r="AD119" s="2"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="20"/>
+      <c r="A120" s="21"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -7006,7 +7134,7 @@
       <c r="AD120" s="2"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="20"/>
+      <c r="A121" s="21"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -7038,7 +7166,7 @@
       <c r="AD121" s="2"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="20"/>
+      <c r="A122" s="21"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -7070,7 +7198,7 @@
       <c r="AD122" s="2"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="20"/>
+      <c r="A123" s="21"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -7102,7 +7230,7 @@
       <c r="AD123" s="2"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="20"/>
+      <c r="A124" s="21"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -7134,7 +7262,7 @@
       <c r="AD124" s="2"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="20"/>
+      <c r="A125" s="21"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -7166,7 +7294,7 @@
       <c r="AD125" s="2"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="20"/>
+      <c r="A126" s="21"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -7198,7 +7326,7 @@
       <c r="AD126" s="2"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="20"/>
+      <c r="A127" s="21"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -7230,7 +7358,7 @@
       <c r="AD127" s="2"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="20"/>
+      <c r="A128" s="21"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -7262,7 +7390,7 @@
       <c r="AD128" s="2"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="20"/>
+      <c r="A129" s="21"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -7294,7 +7422,7 @@
       <c r="AD129" s="2"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="20"/>
+      <c r="A130" s="21"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -7326,7 +7454,7 @@
       <c r="AD130" s="2"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="20"/>
+      <c r="A131" s="21"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -7358,7 +7486,7 @@
       <c r="AD131" s="2"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="20"/>
+      <c r="A132" s="21"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -7390,7 +7518,7 @@
       <c r="AD132" s="2"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="20"/>
+      <c r="A133" s="21"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -7422,7 +7550,7 @@
       <c r="AD133" s="2"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="20"/>
+      <c r="A134" s="21"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -7454,7 +7582,7 @@
       <c r="AD134" s="2"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="20"/>
+      <c r="A135" s="21"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -7486,7 +7614,7 @@
       <c r="AD135" s="2"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="20"/>
+      <c r="A136" s="21"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -7518,7 +7646,7 @@
       <c r="AD136" s="2"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="20"/>
+      <c r="A137" s="21"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -7550,7 +7678,7 @@
       <c r="AD137" s="2"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="20"/>
+      <c r="A138" s="21"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -7582,7 +7710,7 @@
       <c r="AD138" s="2"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="20"/>
+      <c r="A139" s="21"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -7614,7 +7742,7 @@
       <c r="AD139" s="2"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="20"/>
+      <c r="A140" s="21"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -7646,7 +7774,7 @@
       <c r="AD140" s="2"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="20"/>
+      <c r="A141" s="21"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -7678,7 +7806,7 @@
       <c r="AD141" s="2"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="20"/>
+      <c r="A142" s="21"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -7710,7 +7838,7 @@
       <c r="AD142" s="2"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="20"/>
+      <c r="A143" s="21"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -7742,7 +7870,7 @@
       <c r="AD143" s="2"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="20"/>
+      <c r="A144" s="21"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -7774,7 +7902,7 @@
       <c r="AD144" s="2"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="20"/>
+      <c r="A145" s="21"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -7806,7 +7934,7 @@
       <c r="AD145" s="2"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="20"/>
+      <c r="A146" s="21"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -7838,7 +7966,7 @@
       <c r="AD146" s="2"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="20"/>
+      <c r="A147" s="21"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -7870,7 +7998,7 @@
       <c r="AD147" s="2"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="20"/>
+      <c r="A148" s="21"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -7902,7 +8030,7 @@
       <c r="AD148" s="2"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="20"/>
+      <c r="A149" s="21"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -7934,7 +8062,7 @@
       <c r="AD149" s="2"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="20"/>
+      <c r="A150" s="21"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -7966,7 +8094,7 @@
       <c r="AD150" s="2"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="20"/>
+      <c r="A151" s="21"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -7998,7 +8126,7 @@
       <c r="AD151" s="2"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="20"/>
+      <c r="A152" s="21"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -8030,7 +8158,7 @@
       <c r="AD152" s="2"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="20"/>
+      <c r="A153" s="21"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -8062,7 +8190,7 @@
       <c r="AD153" s="2"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="20"/>
+      <c r="A154" s="21"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -8094,7 +8222,7 @@
       <c r="AD154" s="2"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="20"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -8126,7 +8254,7 @@
       <c r="AD155" s="2"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="20"/>
+      <c r="A156" s="21"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -8158,7 +8286,7 @@
       <c r="AD156" s="2"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="20"/>
+      <c r="A157" s="21"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -8190,7 +8318,7 @@
       <c r="AD157" s="2"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="20"/>
+      <c r="A158" s="21"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -8222,7 +8350,7 @@
       <c r="AD158" s="2"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="20"/>
+      <c r="A159" s="21"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -8254,7 +8382,7 @@
       <c r="AD159" s="2"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="20"/>
+      <c r="A160" s="21"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -8286,7 +8414,7 @@
       <c r="AD160" s="2"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="20"/>
+      <c r="A161" s="21"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -8318,7 +8446,7 @@
       <c r="AD161" s="2"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="20"/>
+      <c r="A162" s="21"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -8350,7 +8478,7 @@
       <c r="AD162" s="2"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="20"/>
+      <c r="A163" s="21"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -8382,7 +8510,7 @@
       <c r="AD163" s="2"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="20"/>
+      <c r="A164" s="21"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -8414,7 +8542,7 @@
       <c r="AD164" s="2"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="20"/>
+      <c r="A165" s="21"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -8446,7 +8574,7 @@
       <c r="AD165" s="2"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="20"/>
+      <c r="A166" s="21"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -8478,7 +8606,7 @@
       <c r="AD166" s="2"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="20"/>
+      <c r="A167" s="21"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -8510,7 +8638,7 @@
       <c r="AD167" s="2"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="20"/>
+      <c r="A168" s="21"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -8542,7 +8670,7 @@
       <c r="AD168" s="2"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="20"/>
+      <c r="A169" s="21"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -8574,7 +8702,7 @@
       <c r="AD169" s="2"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="20"/>
+      <c r="A170" s="21"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -8606,7 +8734,7 @@
       <c r="AD170" s="2"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="20"/>
+      <c r="A171" s="21"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -8638,7 +8766,7 @@
       <c r="AD171" s="2"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="20"/>
+      <c r="A172" s="21"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -8670,7 +8798,7 @@
       <c r="AD172" s="2"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="20"/>
+      <c r="A173" s="21"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -8702,7 +8830,7 @@
       <c r="AD173" s="2"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="20"/>
+      <c r="A174" s="21"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -8734,7 +8862,7 @@
       <c r="AD174" s="2"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="20"/>
+      <c r="A175" s="21"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -8766,7 +8894,7 @@
       <c r="AD175" s="2"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="20"/>
+      <c r="A176" s="21"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -8798,7 +8926,7 @@
       <c r="AD176" s="2"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="20"/>
+      <c r="A177" s="21"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -8830,7 +8958,7 @@
       <c r="AD177" s="2"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="20"/>
+      <c r="A178" s="21"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -8862,7 +8990,7 @@
       <c r="AD178" s="2"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="20"/>
+      <c r="A179" s="21"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -8894,7 +9022,7 @@
       <c r="AD179" s="2"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="20"/>
+      <c r="A180" s="21"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -8926,7 +9054,7 @@
       <c r="AD180" s="2"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="20"/>
+      <c r="A181" s="21"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -8958,7 +9086,7 @@
       <c r="AD181" s="2"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="20"/>
+      <c r="A182" s="21"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -8990,7 +9118,7 @@
       <c r="AD182" s="2"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="20"/>
+      <c r="A183" s="21"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -9022,7 +9150,7 @@
       <c r="AD183" s="2"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="20"/>
+      <c r="A184" s="21"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -9054,7 +9182,7 @@
       <c r="AD184" s="2"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="20"/>
+      <c r="A185" s="21"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -9086,7 +9214,7 @@
       <c r="AD185" s="2"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="20"/>
+      <c r="A186" s="21"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -9118,7 +9246,7 @@
       <c r="AD186" s="2"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="20"/>
+      <c r="A187" s="21"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -9150,7 +9278,7 @@
       <c r="AD187" s="2"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="20"/>
+      <c r="A188" s="21"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -9182,7 +9310,7 @@
       <c r="AD188" s="2"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="20"/>
+      <c r="A189" s="21"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -9214,7 +9342,7 @@
       <c r="AD189" s="2"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="20"/>
+      <c r="A190" s="21"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -9246,7 +9374,7 @@
       <c r="AD190" s="2"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="20"/>
+      <c r="A191" s="21"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -9278,7 +9406,7 @@
       <c r="AD191" s="2"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="20"/>
+      <c r="A192" s="21"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -9310,7 +9438,7 @@
       <c r="AD192" s="2"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="20"/>
+      <c r="A193" s="21"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -9342,7 +9470,7 @@
       <c r="AD193" s="2"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="20"/>
+      <c r="A194" s="21"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -9374,7 +9502,7 @@
       <c r="AD194" s="2"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="20"/>
+      <c r="A195" s="21"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -9406,7 +9534,7 @@
       <c r="AD195" s="2"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="20"/>
+      <c r="A196" s="21"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -9438,7 +9566,7 @@
       <c r="AD196" s="2"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="20"/>
+      <c r="A197" s="21"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -9470,7 +9598,7 @@
       <c r="AD197" s="2"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="20"/>
+      <c r="A198" s="21"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -9502,7 +9630,7 @@
       <c r="AD198" s="2"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="20"/>
+      <c r="A199" s="21"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -9534,7 +9662,7 @@
       <c r="AD199" s="2"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="20"/>
+      <c r="A200" s="21"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -9566,7 +9694,7 @@
       <c r="AD200" s="2"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="20"/>
+      <c r="A201" s="21"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -9598,7 +9726,7 @@
       <c r="AD201" s="2"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="20"/>
+      <c r="A202" s="21"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -9630,7 +9758,7 @@
       <c r="AD202" s="2"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="20"/>
+      <c r="A203" s="21"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -9662,7 +9790,7 @@
       <c r="AD203" s="2"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="20"/>
+      <c r="A204" s="21"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -9694,7 +9822,7 @@
       <c r="AD204" s="2"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="20"/>
+      <c r="A205" s="21"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -9726,7 +9854,7 @@
       <c r="AD205" s="2"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="20"/>
+      <c r="A206" s="21"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -9758,7 +9886,7 @@
       <c r="AD206" s="2"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="20"/>
+      <c r="A207" s="21"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -9790,7 +9918,7 @@
       <c r="AD207" s="2"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="20"/>
+      <c r="A208" s="21"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -9822,7 +9950,7 @@
       <c r="AD208" s="2"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="20"/>
+      <c r="A209" s="21"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -9854,7 +9982,7 @@
       <c r="AD209" s="2"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="20"/>
+      <c r="A210" s="21"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -9886,7 +10014,7 @@
       <c r="AD210" s="2"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="20"/>
+      <c r="A211" s="21"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -9918,7 +10046,7 @@
       <c r="AD211" s="2"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="20"/>
+      <c r="A212" s="21"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -9950,7 +10078,7 @@
       <c r="AD212" s="2"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="20"/>
+      <c r="A213" s="21"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -9982,7 +10110,7 @@
       <c r="AD213" s="2"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="20"/>
+      <c r="A214" s="21"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -10014,7 +10142,7 @@
       <c r="AD214" s="2"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="20"/>
+      <c r="A215" s="21"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -10046,7 +10174,7 @@
       <c r="AD215" s="2"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="20"/>
+      <c r="A216" s="21"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -10078,7 +10206,7 @@
       <c r="AD216" s="2"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="20"/>
+      <c r="A217" s="21"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -10110,7 +10238,7 @@
       <c r="AD217" s="2"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="20"/>
+      <c r="A218" s="21"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -10142,7 +10270,7 @@
       <c r="AD218" s="2"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="20"/>
+      <c r="A219" s="21"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -10174,7 +10302,7 @@
       <c r="AD219" s="2"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="20"/>
+      <c r="A220" s="21"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -10206,7 +10334,7 @@
       <c r="AD220" s="2"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="20"/>
+      <c r="A221" s="21"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -10238,7 +10366,7 @@
       <c r="AD221" s="2"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="20"/>
+      <c r="A222" s="21"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -10270,7 +10398,7 @@
       <c r="AD222" s="2"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="20"/>
+      <c r="A223" s="21"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
@@ -10302,7 +10430,7 @@
       <c r="AD223" s="2"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="20"/>
+      <c r="A224" s="21"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
@@ -10334,7 +10462,7 @@
       <c r="AD224" s="2"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="20"/>
+      <c r="A225" s="21"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
@@ -10366,7 +10494,7 @@
       <c r="AD225" s="2"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="20"/>
+      <c r="A226" s="21"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
@@ -10398,7 +10526,7 @@
       <c r="AD226" s="2"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="20"/>
+      <c r="A227" s="21"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
@@ -10430,7 +10558,7 @@
       <c r="AD227" s="2"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="20"/>
+      <c r="A228" s="21"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
@@ -10462,7 +10590,7 @@
       <c r="AD228" s="2"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="20"/>
+      <c r="A229" s="21"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
@@ -10494,7 +10622,7 @@
       <c r="AD229" s="2"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="20"/>
+      <c r="A230" s="21"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
@@ -10526,7 +10654,7 @@
       <c r="AD230" s="2"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="20"/>
+      <c r="A231" s="21"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
@@ -10558,7 +10686,7 @@
       <c r="AD231" s="2"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="20"/>
+      <c r="A232" s="21"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
@@ -10590,7 +10718,7 @@
       <c r="AD232" s="2"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="20"/>
+      <c r="A233" s="21"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
@@ -10622,7 +10750,7 @@
       <c r="AD233" s="2"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="20"/>
+      <c r="A234" s="21"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
@@ -10654,7 +10782,7 @@
       <c r="AD234" s="2"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="20"/>
+      <c r="A235" s="21"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
@@ -10686,7 +10814,7 @@
       <c r="AD235" s="2"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="20"/>
+      <c r="A236" s="21"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
@@ -10718,7 +10846,7 @@
       <c r="AD236" s="2"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="20"/>
+      <c r="A237" s="21"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
@@ -10750,7 +10878,7 @@
       <c r="AD237" s="2"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="20"/>
+      <c r="A238" s="21"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
@@ -10782,7 +10910,7 @@
       <c r="AD238" s="2"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="20"/>
+      <c r="A239" s="21"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
@@ -10814,7 +10942,7 @@
       <c r="AD239" s="2"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="20"/>
+      <c r="A240" s="21"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
@@ -10846,7 +10974,7 @@
       <c r="AD240" s="2"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="20"/>
+      <c r="A241" s="21"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
@@ -10878,7 +11006,7 @@
       <c r="AD241" s="2"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="20"/>
+      <c r="A242" s="21"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
@@ -10910,7 +11038,7 @@
       <c r="AD242" s="2"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="20"/>
+      <c r="A243" s="21"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -10942,7 +11070,7 @@
       <c r="AD243" s="2"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="20"/>
+      <c r="A244" s="21"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
@@ -10974,7 +11102,7 @@
       <c r="AD244" s="2"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="20"/>
+      <c r="A245" s="21"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
@@ -11006,7 +11134,7 @@
       <c r="AD245" s="2"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="20"/>
+      <c r="A246" s="21"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
@@ -11038,7 +11166,7 @@
       <c r="AD246" s="2"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="20"/>
+      <c r="A247" s="21"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -11070,7 +11198,7 @@
       <c r="AD247" s="2"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="20"/>
+      <c r="A248" s="21"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
@@ -11102,7 +11230,7 @@
       <c r="AD248" s="2"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="20"/>
+      <c r="A249" s="21"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -11134,7 +11262,7 @@
       <c r="AD249" s="2"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="20"/>
+      <c r="A250" s="21"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
@@ -11166,7 +11294,7 @@
       <c r="AD250" s="2"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="20"/>
+      <c r="A251" s="21"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
@@ -11198,7 +11326,7 @@
       <c r="AD251" s="2"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="20"/>
+      <c r="A252" s="21"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
@@ -11230,7 +11358,7 @@
       <c r="AD252" s="2"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="20"/>
+      <c r="A253" s="21"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
@@ -11262,7 +11390,7 @@
       <c r="AD253" s="2"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="20"/>
+      <c r="A254" s="21"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -11294,7 +11422,7 @@
       <c r="AD254" s="2"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="20"/>
+      <c r="A255" s="21"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
@@ -11326,7 +11454,7 @@
       <c r="AD255" s="2"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="20"/>
+      <c r="A256" s="21"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -11358,7 +11486,7 @@
       <c r="AD256" s="2"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="20"/>
+      <c r="A257" s="21"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
@@ -11390,7 +11518,7 @@
       <c r="AD257" s="2"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="20"/>
+      <c r="A258" s="21"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
@@ -11422,7 +11550,7 @@
       <c r="AD258" s="2"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="20"/>
+      <c r="A259" s="21"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
@@ -11454,7 +11582,7 @@
       <c r="AD259" s="2"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="20"/>
+      <c r="A260" s="21"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
@@ -11486,7 +11614,7 @@
       <c r="AD260" s="2"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="20"/>
+      <c r="A261" s="21"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
@@ -11518,7 +11646,7 @@
       <c r="AD261" s="2"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="20"/>
+      <c r="A262" s="21"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
@@ -11550,7 +11678,7 @@
       <c r="AD262" s="2"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="20"/>
+      <c r="A263" s="21"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
@@ -11582,7 +11710,7 @@
       <c r="AD263" s="2"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="20"/>
+      <c r="A264" s="21"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
@@ -11614,7 +11742,7 @@
       <c r="AD264" s="2"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="20"/>
+      <c r="A265" s="21"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
@@ -11646,7 +11774,7 @@
       <c r="AD265" s="2"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="20"/>
+      <c r="A266" s="21"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
@@ -11678,7 +11806,7 @@
       <c r="AD266" s="2"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="20"/>
+      <c r="A267" s="21"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
@@ -11710,7 +11838,7 @@
       <c r="AD267" s="2"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="20"/>
+      <c r="A268" s="21"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
@@ -11742,7 +11870,7 @@
       <c r="AD268" s="2"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="20"/>
+      <c r="A269" s="21"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
@@ -11774,7 +11902,7 @@
       <c r="AD269" s="2"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="20"/>
+      <c r="A270" s="21"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
@@ -11806,7 +11934,7 @@
       <c r="AD270" s="2"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="20"/>
+      <c r="A271" s="21"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
@@ -11838,7 +11966,7 @@
       <c r="AD271" s="2"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="20"/>
+      <c r="A272" s="21"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
@@ -11870,7 +11998,7 @@
       <c r="AD272" s="2"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="20"/>
+      <c r="A273" s="21"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -11902,7 +12030,7 @@
       <c r="AD273" s="2"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="20"/>
+      <c r="A274" s="21"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
@@ -11934,7 +12062,7 @@
       <c r="AD274" s="2"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="20"/>
+      <c r="A275" s="21"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
@@ -11966,7 +12094,7 @@
       <c r="AD275" s="2"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="20"/>
+      <c r="A276" s="21"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
@@ -11998,7 +12126,7 @@
       <c r="AD276" s="2"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="20"/>
+      <c r="A277" s="21"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
@@ -12030,7 +12158,7 @@
       <c r="AD277" s="2"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="20"/>
+      <c r="A278" s="21"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
@@ -12062,7 +12190,7 @@
       <c r="AD278" s="2"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="20"/>
+      <c r="A279" s="21"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
@@ -12094,7 +12222,7 @@
       <c r="AD279" s="2"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="20"/>
+      <c r="A280" s="21"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
@@ -12126,7 +12254,7 @@
       <c r="AD280" s="2"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="20"/>
+      <c r="A281" s="21"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
@@ -12158,7 +12286,7 @@
       <c r="AD281" s="2"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="20"/>
+      <c r="A282" s="21"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
@@ -12190,7 +12318,7 @@
       <c r="AD282" s="2"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="20"/>
+      <c r="A283" s="21"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
@@ -12222,7 +12350,7 @@
       <c r="AD283" s="2"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="20"/>
+      <c r="A284" s="21"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
@@ -12254,7 +12382,7 @@
       <c r="AD284" s="2"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="20"/>
+      <c r="A285" s="21"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
@@ -12286,7 +12414,7 @@
       <c r="AD285" s="2"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="20"/>
+      <c r="A286" s="21"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
@@ -12318,7 +12446,7 @@
       <c r="AD286" s="2"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="20"/>
+      <c r="A287" s="21"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
       <c r="D287" s="2"/>
@@ -12350,7 +12478,7 @@
       <c r="AD287" s="2"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="20"/>
+      <c r="A288" s="21"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
       <c r="D288" s="2"/>
@@ -12382,7 +12510,7 @@
       <c r="AD288" s="2"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="20"/>
+      <c r="A289" s="21"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
@@ -12414,7 +12542,7 @@
       <c r="AD289" s="2"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="20"/>
+      <c r="A290" s="21"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
@@ -12446,7 +12574,7 @@
       <c r="AD290" s="2"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="20"/>
+      <c r="A291" s="21"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
@@ -12478,7 +12606,7 @@
       <c r="AD291" s="2"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="20"/>
+      <c r="A292" s="21"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
       <c r="D292" s="2"/>
@@ -12510,7 +12638,7 @@
       <c r="AD292" s="2"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="20"/>
+      <c r="A293" s="21"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
       <c r="D293" s="2"/>
@@ -12542,7 +12670,7 @@
       <c r="AD293" s="2"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="20"/>
+      <c r="A294" s="21"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
       <c r="D294" s="2"/>
@@ -12574,7 +12702,7 @@
       <c r="AD294" s="2"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="20"/>
+      <c r="A295" s="21"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
@@ -12606,7 +12734,7 @@
       <c r="AD295" s="2"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="20"/>
+      <c r="A296" s="21"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
@@ -12638,7 +12766,7 @@
       <c r="AD296" s="2"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="20"/>
+      <c r="A297" s="21"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
       <c r="D297" s="2"/>
@@ -12670,7 +12798,7 @@
       <c r="AD297" s="2"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="20"/>
+      <c r="A298" s="21"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
       <c r="D298" s="2"/>
@@ -12702,7 +12830,7 @@
       <c r="AD298" s="2"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="20"/>
+      <c r="A299" s="21"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
       <c r="D299" s="2"/>
@@ -12734,7 +12862,7 @@
       <c r="AD299" s="2"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="2"/>
+      <c r="A300" s="21"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
       <c r="D300" s="2"/>
@@ -35645,6 +35773,38 @@
       <c r="AC1015" s="2"/>
       <c r="AD1015" s="2"/>
     </row>
+    <row r="1016" ht="15.75" customHeight="1">
+      <c r="A1016" s="2"/>
+      <c r="B1016" s="2"/>
+      <c r="C1016" s="2"/>
+      <c r="D1016" s="2"/>
+      <c r="E1016" s="2"/>
+      <c r="F1016" s="2"/>
+      <c r="G1016" s="2"/>
+      <c r="H1016" s="2"/>
+      <c r="I1016" s="2"/>
+      <c r="J1016" s="2"/>
+      <c r="K1016" s="2"/>
+      <c r="L1016" s="2"/>
+      <c r="M1016" s="2"/>
+      <c r="N1016" s="2"/>
+      <c r="O1016" s="2"/>
+      <c r="P1016" s="2"/>
+      <c r="Q1016" s="2"/>
+      <c r="R1016" s="2"/>
+      <c r="S1016" s="2"/>
+      <c r="T1016" s="2"/>
+      <c r="U1016" s="2"/>
+      <c r="V1016" s="2"/>
+      <c r="W1016" s="2"/>
+      <c r="X1016" s="2"/>
+      <c r="Y1016" s="2"/>
+      <c r="Z1016" s="2"/>
+      <c r="AA1016" s="2"/>
+      <c r="AB1016" s="2"/>
+      <c r="AC1016" s="2"/>
+      <c r="AD1016" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
